--- a/AtchisonRegime/Outputs/USA/USA500_Info_Tech/df_regSummary_USA500_Info_Tech.xlsx
+++ b/AtchisonRegime/Outputs/USA/USA500_Info_Tech/df_regSummary_USA500_Info_Tech.xlsx
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G2" t="n">
-        <v>2.093851115554846</v>
+        <v>2.043950641208566</v>
       </c>
       <c r="H2" t="n">
-        <v>4.267889535836972</v>
+        <v>4.251819175111586</v>
       </c>
       <c r="I2" t="n">
         <v>-9.03342228644261</v>
@@ -545,16 +545,16 @@
         <v>13.0963168927553</v>
       </c>
       <c r="K2" t="n">
-        <v>38.75</v>
+        <v>39.1304347826087</v>
       </c>
       <c r="L2" t="n">
         <v>5</v>
       </c>
       <c r="M2" t="n">
-        <v>12.4</v>
+        <v>12.6</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3013602524333251</v>
+        <v>0.2984125510387441</v>
       </c>
       <c r="O2" t="n">
         <v>0.0376879500447278</v>
@@ -603,7 +603,7 @@
         <v>10.24694135888</v>
       </c>
       <c r="K3" t="n">
-        <v>20</v>
+        <v>19.87577639751553</v>
       </c>
       <c r="L3" t="n">
         <v>5</v>
@@ -661,7 +661,7 @@
         <v>11.138619523777</v>
       </c>
       <c r="K4" t="n">
-        <v>20</v>
+        <v>19.87577639751553</v>
       </c>
       <c r="L4" t="n">
         <v>4</v>
@@ -719,7 +719,7 @@
         <v>11.8700581470654</v>
       </c>
       <c r="K5" t="n">
-        <v>21.25</v>
+        <v>21.11801242236025</v>
       </c>
       <c r="L5" t="n">
         <v>4</v>
